--- a/data/Interrogation.xlsx
+++ b/data/Interrogation.xlsx
@@ -1,102 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:workbookPr codeName="ThisWorkbook"/>
-  <s:bookViews>
-    <s:workbookView activeTab="3"/>
-  </s:bookViews>
-  <s:sheets>
-    <s:sheet name="getDiseaseList" sheetId="1" r:id="rId1"/>
-    <s:sheet name="getDrugList" sheetId="2" r:id="rId2"/>
-    <s:sheet name="syncDoctorList" sheetId="3" r:id="rId3"/>
-    <s:sheet name="saveOrderByAfter" sheetId="4" r:id="rId4"/>
-  </s:sheets>
-  <s:definedNames/>
-  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
-</s:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
-  <si>
-    <t>case_id</t>
-  </si>
-  <si>
-    <t>interface</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>expected</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>check_sql</t>
-  </si>
-  <si>
-    <t>getDiseaseList</t>
-  </si>
-  <si>
-    <t>获取病症列表-获取成功</t>
-  </si>
-  <si>
-    <t>post</t>
-  </si>
-  <si>
-    <t>/Inquiry</t>
-  </si>
-  <si>
-    <t>{"QueryType": "getDiseaseList","Params": '{"LASTTIME":0}'}</t>
-  </si>
-  <si>
-    <t>{"result": "0000", "msg": "获取成功"}</t>
-  </si>
-  <si>
-    <t>通过</t>
-  </si>
-  <si>
-    <t>getDrugList</t>
-  </si>
-  <si>
-    <t>搜索药品-获取成功</t>
-  </si>
-  <si>
-    <t>{"QueryType": "getDrugList","Params": '{"page":1,"keyword":"#drugs#","barcode":""}'}</t>
-  </si>
-  <si>
-    <t>syncDoctorList</t>
-  </si>
-  <si>
-    <t>获取医生列表-获取成功</t>
-  </si>
-  <si>
-    <t>{"QueryType": "syncDoctorList","Params": '{"keyword":""}'}</t>
-  </si>
-  <si>
-    <t>saveOrderByAfter</t>
-  </si>
-  <si>
-    <t>提交预约问诊-获取成功</t>
-  </si>
-  <si>
-    <t>{"QueryType": "saveOrderByAfter","Params": '{"recipe":[{"COUNTS":"2","NUMBER":"1","UNITIDS":"粒","TIMES":"3","goodsprice":"","USAGE":"口服","DAYS":"1","goodsname":"#goodsname#","id":"#drugs_id#","spec":"0.25g10粒3板"}],"userInfo":{"name":"张三","symptom":"4","phone":"13012345678","age":"30","sex":1,"symptomName":"感冒"},"depict":{"condition":"流鼻涕","record":""},"doctorId":"#doctorId#","doctorPhone":"#doctorPhone#"}'}</t>
-  </si>
-  <si>
-    <t>{"result": "0000", "msg": "提交成功"}</t>
-  </si>
-</sst>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="getDiseaseList" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="getDrugList" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="syncDoctorList" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="saveOrderByAfter" sheetId="4" state="visible" r:id="rId4"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -152,25 +69,24 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" builtinId="0" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -443,7 +359,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -452,59 +368,91 @@
     <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>interface</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>expected</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>check_sql</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>getDiseaseList</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>获取病症列表-获取成功</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>/Inquiry</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>{"QueryType": "getDiseaseList","Params": '{"LASTTIME":0}'}</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{"result": "0000", "msg": "获取成功"}</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -520,7 +468,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -530,59 +478,91 @@
     <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>interface</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>expected</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>check_sql</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>getDrugList</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>搜索药品-获取成功</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>/Inquiry</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>{"QueryType": "getDrugList","Params": '{"page":1,"keyword":"#drugs#","barcode":""}'}</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{"result": "0000", "msg": "获取成功"}</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -597,7 +577,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -606,59 +586,91 @@
     <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>interface</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>expected</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>check_sql</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>syncDoctorList</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>获取医生列表-获取成功</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>/Inquiry</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>{"QueryType": "syncDoctorList","Params": '{"keyword":""}'}</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{"result": "0000", "msg": "获取成功"}</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -674,7 +686,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="16.375" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -684,59 +696,91 @@
     <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>interface</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>expected</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>check_sql</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="42.75" customHeight="1">
+    <row r="2" ht="42.75" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>saveOrderByAfter</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>提交预约问诊-获取成功</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>/Inquiry</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>{"QueryType": "saveOrderByAfter","Params": '{"recipe":[{"COUNTS":"2","NUMBER":"1","UNITIDS":"粒","TIMES":"3","goodsprice":"","USAGE":"口服","DAYS":"1","goodsname":"#goodsname#","id":"#drugs_id#","spec":"0.25g10粒3板"}],"userInfo":{"name":"张三","symptom":"4","phone":"13012345678","age":"30","sex":1,"symptomName":"感冒"},"depict":{"condition":"流鼻涕","record":""},"doctorId":"#doctorId#","doctorPhone":"#doctorPhone#"}'}</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{"result": "0000", "msg": "提交成功"}</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/Interrogation.xlsx
+++ b/data/Interrogation.xlsx
@@ -1,19 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="getDiseaseList" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="getDrugList" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="syncDoctorList" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="saveOrderByAfter" sheetId="4" state="visible" r:id="rId4"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:workbookPr codeName="ThisWorkbook"/>
+  <s:bookViews>
+    <s:workbookView activeTab="3"/>
+  </s:bookViews>
+  <s:sheets>
+    <s:sheet name="getDiseaseList" sheetId="1" r:id="rId1"/>
+    <s:sheet name="getDrugList" sheetId="2" r:id="rId2"/>
+    <s:sheet name="syncDoctorList" sheetId="3" r:id="rId3"/>
+    <s:sheet name="saveOrderByAfter" sheetId="4" r:id="rId4"/>
+  </s:sheets>
+  <s:definedNames/>
+  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
+</s:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
+  <si>
+    <t>case_id</t>
+  </si>
+  <si>
+    <t>interface</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>expected</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>check_sql</t>
+  </si>
+  <si>
+    <t>getDiseaseList</t>
+  </si>
+  <si>
+    <t>获取病症列表-获取成功</t>
+  </si>
+  <si>
+    <t>post</t>
+  </si>
+  <si>
+    <t>/Inquiry</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getDiseaseList","Params": '{"LASTTIME":0}'}</t>
+  </si>
+  <si>
+    <t>{"result": "0000", "msg": "获取成功"}</t>
+  </si>
+  <si>
+    <t>通过</t>
+  </si>
+  <si>
+    <t>getDrugList</t>
+  </si>
+  <si>
+    <t>搜索药品-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getDrugList","Params": '{"page":1,"keyword":"#drugs#","barcode":""}'}</t>
+  </si>
+  <si>
+    <t>syncDoctorList</t>
+  </si>
+  <si>
+    <t>获取医生列表-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "syncDoctorList","Params": '{"keyword":""}'}</t>
+  </si>
+  <si>
+    <t>saveOrderByAfter</t>
+  </si>
+  <si>
+    <t>提交预约问诊-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "saveOrderByAfter","Params": '{"recipe":[{"COUNTS":"2","NUMBER":"1","UNITIDS":"粒","TIMES":"3","goodsprice":"","USAGE":"口服","DAYS":"1","goodsname":"#goodsname#","id":"#drugs_id#","spec":"0.25g10粒3板"}],"userInfo":{"name":"张三","symptom":"4","phone":"13012345678","age":"30","sex":1,"symptomName":"感冒"},"depict":{"condition":"流鼻涕","record":""},"doctorId":"#doctorId#","doctorPhone":"#doctorPhone#"}'}</t>
+  </si>
+  <si>
+    <t>{"result": "0000", "msg": "提交成功"}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,24 +152,25 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" builtinId="0" xfId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -359,7 +443,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
     <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -368,91 +452,59 @@
     <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>case_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>interface</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>expected</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>check_sql</t>
-        </is>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>getDiseaseList</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>获取病症列表-获取成功</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>/Inquiry</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>{"QueryType": "getDiseaseList","Params": '{"LASTTIME":0}'}</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{"result": "0000", "msg": "获取成功"}</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -468,7 +520,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
     <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -478,91 +530,59 @@
     <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>case_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>interface</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>expected</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>check_sql</t>
-        </is>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>getDrugList</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>搜索药品-获取成功</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>/Inquiry</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>{"QueryType": "getDrugList","Params": '{"page":1,"keyword":"#drugs#","barcode":""}'}</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{"result": "0000", "msg": "获取成功"}</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -577,7 +597,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
     <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -586,91 +606,59 @@
     <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>case_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>interface</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>expected</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>check_sql</t>
-        </is>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>syncDoctorList</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>获取医生列表-获取成功</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>/Inquiry</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>{"QueryType": "syncDoctorList","Params": '{"keyword":""}'}</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{"result": "0000", "msg": "获取成功"}</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -686,7 +674,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
     <col width="16.375" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -696,91 +684,59 @@
     <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>case_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>interface</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>expected</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>check_sql</t>
-        </is>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2" ht="42.75" customHeight="1">
+    <row r="2" spans="1:9" ht="42.75" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>saveOrderByAfter</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>提交预约问诊-获取成功</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>/Inquiry</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>{"QueryType": "saveOrderByAfter","Params": '{"recipe":[{"COUNTS":"2","NUMBER":"1","UNITIDS":"粒","TIMES":"3","goodsprice":"","USAGE":"口服","DAYS":"1","goodsname":"#goodsname#","id":"#drugs_id#","spec":"0.25g10粒3板"}],"userInfo":{"name":"张三","symptom":"4","phone":"13012345678","age":"30","sex":1,"symptomName":"感冒"},"depict":{"condition":"流鼻涕","record":""},"doctorId":"#doctorId#","doctorPhone":"#doctorPhone#"}'}</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{"result": "0000", "msg": "提交成功"}</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
